--- a/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_1.xlsx
+++ b/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_1.xlsx
@@ -362,12 +362,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Sessions</t>
+          <t>PracticeTrials</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>ExamGrade</t>
+          <t>Happiness</t>
         </is>
       </c>
     </row>
@@ -378,10 +378,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>-0.8750908594047946</v>
+        <v>0.3588675039674205</v>
       </c>
       <c r="C2">
-        <v>-1.003329346827337</v>
+        <v>1.29005005240431</v>
       </c>
     </row>
     <row r="3">
@@ -391,10 +391,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>-1.906252757130753</v>
+        <v>-0.8292901304116187</v>
       </c>
       <c r="C3">
-        <v>-1.852469270528959</v>
+        <v>-0.884567176345006</v>
       </c>
     </row>
     <row r="4">
@@ -404,10 +404,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>-0.7606244590074878</v>
+        <v>0.4802616086676383</v>
       </c>
       <c r="C4">
-        <v>-0.8776482360126883</v>
+        <v>0.4649277494043512</v>
       </c>
     </row>
     <row r="5">
@@ -417,10 +417,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>1.064252722270593</v>
+        <v>-0.946105770081146</v>
       </c>
       <c r="C5">
-        <v>1.073382893122801</v>
+        <v>-0.8439627383994124</v>
       </c>
     </row>
     <row r="6">
@@ -430,10 +430,10 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.2602467384493959</v>
+        <v>-0.4798463118498414</v>
       </c>
       <c r="C6">
-        <v>2.219812564539883</v>
+        <v>0.8653891676465557</v>
       </c>
     </row>
     <row r="7">
@@ -443,10 +443,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.254937634036601</v>
+        <v>1.776119268695567</v>
       </c>
       <c r="C7">
-        <v>0.4699603110738944</v>
+        <v>1.326068684225534</v>
       </c>
     </row>
     <row r="8">
@@ -456,10 +456,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>-2.14747309802205</v>
+        <v>2.400723763415977</v>
       </c>
       <c r="C8">
-        <v>-0.7901132774157793</v>
+        <v>1.872661909265424</v>
       </c>
     </row>
     <row r="9">
@@ -469,10 +469,10 @@
         </is>
       </c>
       <c r="B9">
-        <v>-0.3557551487148412</v>
+        <v>-0.3946620553474434</v>
       </c>
       <c r="C9">
-        <v>-0.6539025712047095</v>
+        <v>0.54728376934873</v>
       </c>
     </row>
     <row r="10">
@@ -482,10 +482,10 @@
         </is>
       </c>
       <c r="B10">
-        <v>-0.7492170270480364</v>
+        <v>1.437864307300099</v>
       </c>
       <c r="C10">
-        <v>0.3409019920034693</v>
+        <v>-0.1810883092535687</v>
       </c>
     </row>
     <row r="11">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="B11">
-        <v>-0.3122011096726482</v>
+        <v>1.316034282601856</v>
       </c>
       <c r="C11">
-        <v>-0.6357227937153774</v>
+        <v>-0.2631226856974865</v>
       </c>
     </row>
     <row r="12">
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="B12">
-        <v>0.02697905241474865</v>
+        <v>-0.8883783005791152</v>
       </c>
       <c r="C12">
-        <v>0.2044482807103113</v>
+        <v>0.5302239225009142</v>
       </c>
     </row>
     <row r="13">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="B13">
-        <v>1.465644889321727</v>
+        <v>-1.810164263408854</v>
       </c>
       <c r="C13">
-        <v>-0.6429165187292455</v>
+        <v>1.530621144523359</v>
       </c>
     </row>
     <row r="14">
@@ -534,10 +534,10 @@
         </is>
       </c>
       <c r="B14">
-        <v>0.9382699311358178</v>
+        <v>1.363919787065002</v>
       </c>
       <c r="C14">
-        <v>-1.401105571867121</v>
+        <v>1.056239357749455</v>
       </c>
     </row>
     <row r="15">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="B15">
-        <v>-1.241477101016635</v>
+        <v>-1.320540116649539</v>
       </c>
       <c r="C15">
-        <v>-1.373693878781682</v>
+        <v>0.7846726592400198</v>
       </c>
     </row>
     <row r="16">
@@ -560,10 +560,10 @@
         </is>
       </c>
       <c r="B16">
-        <v>-0.4649847561477554</v>
+        <v>1.86575617707857</v>
       </c>
       <c r="C16">
-        <v>0.6171733825574427</v>
+        <v>1.79409542056051</v>
       </c>
     </row>
     <row r="17">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="B17">
-        <v>-1.55109519740285</v>
+        <v>-1.280315903538557</v>
       </c>
       <c r="C17">
-        <v>-0.9663912795503159</v>
+        <v>-1.148909481980835</v>
       </c>
     </row>
     <row r="18">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B18">
-        <v>2.077215763699273</v>
+        <v>-0.8759116048131377</v>
       </c>
       <c r="C18">
-        <v>1.61052111449262</v>
+        <v>-0.3925475527718243</v>
       </c>
     </row>
     <row r="19">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B19">
-        <v>0.2286076623774843</v>
+        <v>0.07453384471974943</v>
       </c>
       <c r="C19">
-        <v>1.683011252429554</v>
+        <v>-0.04933577637953156</v>
       </c>
     </row>
     <row r="20">
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="B20">
-        <v>0.008936062949364476</v>
+        <v>0.1298367285009582</v>
       </c>
       <c r="C20">
-        <v>-1.097798550633583</v>
+        <v>0.05999195851131646</v>
       </c>
     </row>
     <row r="21">
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B21">
-        <v>0.7962399492336095</v>
+        <v>0.7633811069762322</v>
       </c>
       <c r="C21">
-        <v>2.067678837891654</v>
+        <v>1.234047003392606</v>
       </c>
     </row>
     <row r="22">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="B22">
-        <v>-0.08956655234884826</v>
+        <v>1.222297331714075</v>
       </c>
       <c r="C22">
-        <v>-0.4686382374023506</v>
+        <v>1.090258030482812</v>
       </c>
     </row>
     <row r="23">
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="B23">
-        <v>0.3077002411209737</v>
+        <v>-0.2873032235133632</v>
       </c>
       <c r="C23">
-        <v>-0.1094616456860795</v>
+        <v>1.251550765071926</v>
       </c>
     </row>
     <row r="24">
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="B24">
-        <v>1.445742406947142</v>
+        <v>-0.6408378085259215</v>
       </c>
       <c r="C24">
-        <v>2.020985675674077</v>
+        <v>-0.8888812481110431</v>
       </c>
     </row>
     <row r="25">
@@ -677,10 +677,10 @@
         </is>
       </c>
       <c r="B25">
-        <v>0.5509588801772255</v>
+        <v>0.6548238529437724</v>
       </c>
       <c r="C25">
-        <v>-0.2935180327107432</v>
+        <v>1.10159986715308</v>
       </c>
     </row>
     <row r="26">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B26">
-        <v>0.4559715630617373</v>
+        <v>-0.2971263579697464</v>
       </c>
       <c r="C26">
-        <v>0.2441960981755791</v>
+        <v>-0.7126503860436998</v>
       </c>
     </row>
     <row r="27">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B27">
-        <v>1.137132939361771</v>
+        <v>-1.040192217885171</v>
       </c>
       <c r="C27">
-        <v>0.2610232556955873</v>
+        <v>0.0220432888312409</v>
       </c>
     </row>
     <row r="28">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="B28">
-        <v>-1.226747369757999</v>
+        <v>1.391686701957969</v>
       </c>
       <c r="C28">
-        <v>-1.096953607681002</v>
+        <v>1.242855873264888</v>
       </c>
     </row>
     <row r="29">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="B29">
-        <v>-1.702575665228224</v>
+        <v>0.05327393796708689</v>
       </c>
       <c r="C29">
-        <v>0.3831941522194074</v>
+        <v>0.6232227993628078</v>
       </c>
     </row>
     <row r="30">
@@ -742,10 +742,10 @@
         </is>
       </c>
       <c r="B30">
-        <v>0.6307504212167198</v>
+        <v>-0.9867987540268854</v>
       </c>
       <c r="C30">
-        <v>-0.2469616953081853</v>
+        <v>-2.035471487416669</v>
       </c>
     </row>
     <row r="31">
@@ -755,10 +755,10 @@
         </is>
       </c>
       <c r="B31">
-        <v>-0.8647840771922759</v>
+        <v>-0.2005629270634201</v>
       </c>
       <c r="C31">
-        <v>-0.2776736758402862</v>
+        <v>0.7194367459651437</v>
       </c>
     </row>
     <row r="32">
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="B32">
-        <v>-0.6601137988729994</v>
+        <v>-3.151600001768938</v>
       </c>
       <c r="C32">
-        <v>0.3356096302709899</v>
+        <v>-1.282885266433044</v>
       </c>
     </row>
     <row r="33">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="B33">
-        <v>1.180546313098874</v>
+        <v>-1.497566840935365</v>
       </c>
       <c r="C33">
-        <v>-0.679842881562675</v>
+        <v>-0.7159216829864659</v>
       </c>
     </row>
     <row r="34">
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="B34">
-        <v>-0.479073121117013</v>
+        <v>-0.1914012251671245</v>
       </c>
       <c r="C34">
-        <v>-0.2963590719377431</v>
+        <v>-0.5892278999552696</v>
       </c>
     </row>
     <row r="35">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="B35">
-        <v>-0.2036919554412837</v>
+        <v>-0.7162010472489161</v>
       </c>
       <c r="C35">
-        <v>0.751027322982883</v>
+        <v>-0.00760966344884062</v>
       </c>
     </row>
     <row r="36">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="B36">
-        <v>2.111059548730509</v>
+        <v>0.07719877262070667</v>
       </c>
       <c r="C36">
-        <v>2.720139654461007</v>
+        <v>-1.449749297226322</v>
       </c>
     </row>
     <row r="37">
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="B37">
-        <v>-0.236821970206512</v>
+        <v>-1.02990708684216</v>
       </c>
       <c r="C37">
-        <v>1.015249435062101</v>
+        <v>-0.7233458311683906</v>
       </c>
     </row>
     <row r="38">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="B38">
-        <v>-0.5377591249991375</v>
+        <v>-0.4299143691079077</v>
       </c>
       <c r="C38">
-        <v>-0.5621417155564609</v>
+        <v>-2.016025271621869</v>
       </c>
     </row>
     <row r="39">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="B39">
-        <v>0.4263686187855803</v>
+        <v>-1.857192775861476</v>
       </c>
       <c r="C39">
-        <v>0.2884778005847465</v>
+        <v>-0.3481190925513764</v>
       </c>
     </row>
     <row r="40">
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B40">
-        <v>-1.170049498431175</v>
+        <v>-0.402252337574666</v>
       </c>
       <c r="C40">
-        <v>-1.281864630932286</v>
+        <v>-0.3261145670492112</v>
       </c>
     </row>
     <row r="41">
@@ -885,10 +885,10 @@
         </is>
       </c>
       <c r="B41">
-        <v>0.8500866302073226</v>
+        <v>1.451199983818989</v>
       </c>
       <c r="C41">
-        <v>1.305269081673365</v>
+        <v>-0.3147465383598452</v>
       </c>
     </row>
     <row r="42">
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="B42">
-        <v>-0.3309938458083794</v>
+        <v>0.07224427839500719</v>
       </c>
       <c r="C42">
-        <v>-0.6392103119006199</v>
+        <v>0.6952753020778107</v>
       </c>
     </row>
     <row r="43">
@@ -911,10 +911,10 @@
         </is>
       </c>
       <c r="B43">
-        <v>-0.5572632522125688</v>
+        <v>-0.4798409221853451</v>
       </c>
       <c r="C43">
-        <v>0.4193193135692257</v>
+        <v>-0.1882328340116949</v>
       </c>
     </row>
     <row r="44">
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="B44">
-        <v>0.5785826735774294</v>
+        <v>0.345850447752991</v>
       </c>
       <c r="C44">
-        <v>1.178845844501164</v>
+        <v>0.3988407103196927</v>
       </c>
     </row>
     <row r="45">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="B45">
-        <v>0.5206063274212427</v>
+        <v>1.105012560891123</v>
       </c>
       <c r="C45">
-        <v>-0.5431408404344334</v>
+        <v>-0.9330815363416209</v>
       </c>
     </row>
     <row r="46">
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="B46">
-        <v>2.262808661993472</v>
+        <v>0.8746622415811788</v>
       </c>
       <c r="C46">
-        <v>0.8352832682259524</v>
+        <v>1.372063202629374</v>
       </c>
     </row>
     <row r="47">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="B47">
-        <v>-3.535812121807442</v>
+        <v>1.318438550071907</v>
       </c>
       <c r="C47">
-        <v>0.6128331316351612</v>
+        <v>0.3351148714200425</v>
       </c>
     </row>
     <row r="48">
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="B48">
-        <v>-1.287601693620175</v>
+        <v>-0.007090389820527664</v>
       </c>
       <c r="C48">
-        <v>-0.7202483072039857</v>
+        <v>-1.257382714588482</v>
       </c>
     </row>
     <row r="49">
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="B49">
-        <v>0.2053406406801782</v>
+        <v>0.3534567280376166</v>
       </c>
       <c r="C49">
-        <v>-0.7731105364589127</v>
+        <v>0.3560894477350643</v>
       </c>
     </row>
     <row r="50">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="B50">
-        <v>0.5166970630177233</v>
+        <v>0.9990615062651539</v>
       </c>
       <c r="C50">
-        <v>-1.892444790257391</v>
+        <v>-0.1100801894166265</v>
       </c>
     </row>
     <row r="51">
@@ -1015,10 +1015,10 @@
         </is>
       </c>
       <c r="B51">
-        <v>0.8658808866214811</v>
+        <v>0.05753809254290779</v>
       </c>
       <c r="C51">
-        <v>-0.4989723272054476</v>
+        <v>-1.374893602573409</v>
       </c>
     </row>
     <row r="52">
@@ -1028,10 +1028,10 @@
         </is>
       </c>
       <c r="B52">
-        <v>-0.07900167185243538</v>
+        <v>-0.04257598150279102</v>
       </c>
       <c r="C52">
-        <v>-0.3348860910336124</v>
+        <v>0.8003453522347802</v>
       </c>
     </row>
     <row r="53">
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="B53">
-        <v>-1.772612810068972</v>
+        <v>0.9374921516527341</v>
       </c>
       <c r="C53">
-        <v>-2.278230333725023</v>
+        <v>-0.109959734814022</v>
       </c>
     </row>
     <row r="54">
@@ -1054,10 +1054,10 @@
         </is>
       </c>
       <c r="B54">
-        <v>0.6333831575323635</v>
+        <v>1.047616965482199</v>
       </c>
       <c r="C54">
-        <v>0.7137729911515762</v>
+        <v>1.397434940128231</v>
       </c>
     </row>
     <row r="55">
@@ -1067,10 +1067,10 @@
         </is>
       </c>
       <c r="B55">
-        <v>-0.7139362040337942</v>
+        <v>0.6760156740055381</v>
       </c>
       <c r="C55">
-        <v>-1.255238933620587</v>
+        <v>-0.9297935689821332</v>
       </c>
     </row>
     <row r="56">
@@ -1080,10 +1080,10 @@
         </is>
       </c>
       <c r="B56">
-        <v>0.4596683457855846</v>
+        <v>0.5670833351791784</v>
       </c>
       <c r="C56">
-        <v>-0.5216146263199671</v>
+        <v>1.248217818258204</v>
       </c>
     </row>
     <row r="57">
@@ -1093,10 +1093,10 @@
         </is>
       </c>
       <c r="B57">
-        <v>0.7183325733209766</v>
+        <v>0.2588886918426891</v>
       </c>
       <c r="C57">
-        <v>-0.06854273393268029</v>
+        <v>-2.288039109004877</v>
       </c>
     </row>
     <row r="58">
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="B58">
-        <v>-0.7355900561021911</v>
+        <v>-0.8948743335125849</v>
       </c>
       <c r="C58">
-        <v>-1.514716697533627</v>
+        <v>0.6734606564203897</v>
       </c>
     </row>
     <row r="59">
@@ -1119,10 +1119,10 @@
         </is>
       </c>
       <c r="B59">
-        <v>-0.8048663707300626</v>
+        <v>-0.3225078007123655</v>
       </c>
       <c r="C59">
-        <v>-0.1380259399404919</v>
+        <v>0.7020548659544368</v>
       </c>
     </row>
     <row r="60">
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="B60">
-        <v>-0.4976340409291181</v>
+        <v>1.129095555932731</v>
       </c>
       <c r="C60">
-        <v>0.01894707848805821</v>
+        <v>1.018446521799195</v>
       </c>
     </row>
     <row r="61">
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="B61">
-        <v>0.8476518502870533</v>
+        <v>0.269234615206116</v>
       </c>
       <c r="C61">
-        <v>0.6208271135055281</v>
+        <v>0.949763882680837</v>
       </c>
     </row>
     <row r="62">
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="B62">
-        <v>0.7454718425100098</v>
+        <v>0.9122924937635044</v>
       </c>
       <c r="C62">
-        <v>1.045356444498778</v>
+        <v>0.6489650284435472</v>
       </c>
     </row>
     <row r="63">
@@ -1171,10 +1171,10 @@
         </is>
       </c>
       <c r="B63">
-        <v>-0.1176513770174216</v>
+        <v>0.7635496928463121</v>
       </c>
       <c r="C63">
-        <v>-0.8796864942658539</v>
+        <v>-0.686056151695279</v>
       </c>
     </row>
     <row r="64">
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="B64">
-        <v>0.1893159051876179</v>
+        <v>1.525404737617005</v>
       </c>
       <c r="C64">
-        <v>-1.420522646026793</v>
+        <v>2.285076116356983</v>
       </c>
     </row>
     <row r="65">
@@ -1197,10 +1197,10 @@
         </is>
       </c>
       <c r="B65">
-        <v>0.02639444957081493</v>
+        <v>-1.504488614244615</v>
       </c>
       <c r="C65">
-        <v>-1.683775723293313</v>
+        <v>-0.559051486825498</v>
       </c>
     </row>
     <row r="66">
@@ -1210,10 +1210,10 @@
         </is>
       </c>
       <c r="B66">
-        <v>0.03479834875278071</v>
+        <v>0.05360726999365611</v>
       </c>
       <c r="C66">
-        <v>-0.391644130470045</v>
+        <v>-0.3474841523336217</v>
       </c>
     </row>
     <row r="67">
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="B67">
-        <v>-0.9644963640856553</v>
+        <v>-0.2224009100952265</v>
       </c>
       <c r="C67">
-        <v>-0.2439670392581843</v>
+        <v>0.08117130179227466</v>
       </c>
     </row>
     <row r="68">
@@ -1236,10 +1236,10 @@
         </is>
       </c>
       <c r="B68">
-        <v>-0.1472443020010948</v>
+        <v>0.4561749171377062</v>
       </c>
       <c r="C68">
-        <v>-2.111830026815529</v>
+        <v>-1.232998598399327</v>
       </c>
     </row>
     <row r="69">
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="B69">
-        <v>0.7293571990954503</v>
+        <v>1.55249612493339</v>
       </c>
       <c r="C69">
-        <v>-0.5587988556619824</v>
+        <v>0.05598771652839263</v>
       </c>
     </row>
     <row r="70">
@@ -1262,10 +1262,10 @@
         </is>
       </c>
       <c r="B70">
-        <v>-0.1656990152430585</v>
+        <v>-0.3329309888938171</v>
       </c>
       <c r="C70">
-        <v>0.3379410477960482</v>
+        <v>-0.1486918259987065</v>
       </c>
     </row>
     <row r="71">
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="B71">
-        <v>0.2657343513998696</v>
+        <v>0.8615506225320094</v>
       </c>
       <c r="C71">
-        <v>0.3719485730824523</v>
+        <v>0.5530990071593539</v>
       </c>
     </row>
     <row r="72">
@@ -1288,10 +1288,10 @@
         </is>
       </c>
       <c r="B72">
-        <v>-1.332443672987984</v>
+        <v>1.212821702525538</v>
       </c>
       <c r="C72">
-        <v>-0.5726333877277947</v>
+        <v>0.4215726799290438</v>
       </c>
     </row>
     <row r="73">
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="B73">
-        <v>-0.3327455826886165</v>
+        <v>0.9483385837833301</v>
       </c>
       <c r="C73">
-        <v>-0.2667930192874292</v>
+        <v>-1.693664796674172</v>
       </c>
     </row>
     <row r="74">
@@ -1314,10 +1314,10 @@
         </is>
       </c>
       <c r="B74">
-        <v>-0.7156378369255785</v>
+        <v>0.03052575509153073</v>
       </c>
       <c r="C74">
-        <v>-1.32586680374925</v>
+        <v>-1.457516743197491</v>
       </c>
     </row>
     <row r="75">
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="B75">
-        <v>-1.035936329468003</v>
+        <v>-0.4630978639453176</v>
       </c>
       <c r="C75">
-        <v>-1.306191174936747</v>
+        <v>-0.6379535185762835</v>
       </c>
     </row>
     <row r="76">
@@ -1340,10 +1340,10 @@
         </is>
       </c>
       <c r="B76">
-        <v>1.048824727382232</v>
+        <v>-0.7218101327655034</v>
       </c>
       <c r="C76">
-        <v>0.7452409765716546</v>
+        <v>0.5047193970238575</v>
       </c>
     </row>
     <row r="77">
@@ -1353,10 +1353,10 @@
         </is>
       </c>
       <c r="B77">
-        <v>0.100889351927484</v>
+        <v>0.5326858115951115</v>
       </c>
       <c r="C77">
-        <v>-0.6266468501731228</v>
+        <v>0.2233032093731968</v>
       </c>
     </row>
     <row r="78">
@@ -1366,10 +1366,10 @@
         </is>
       </c>
       <c r="B78">
-        <v>0.6343435105502406</v>
+        <v>-0.6036456873424454</v>
       </c>
       <c r="C78">
-        <v>-0.8326545239851134</v>
+        <v>1.05280634636916</v>
       </c>
     </row>
     <row r="79">
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="B79">
-        <v>-0.6755777922197079</v>
+        <v>0.7435966593144259</v>
       </c>
       <c r="C79">
-        <v>-0.1225442248799713</v>
+        <v>1.596371860981898</v>
       </c>
     </row>
     <row r="80">
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="B80">
-        <v>0.3662740808884639</v>
+        <v>-0.4070627887292286</v>
       </c>
       <c r="C80">
-        <v>0.0006269506372171829</v>
+        <v>-1.263085066911795</v>
       </c>
     </row>
     <row r="81">
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="B81">
-        <v>-0.9083162227355539</v>
+        <v>-0.5321337051890911</v>
       </c>
       <c r="C81">
-        <v>-1.825581025448133</v>
+        <v>0.5928206702837487</v>
       </c>
     </row>
     <row r="82">
@@ -1418,10 +1418,10 @@
         </is>
       </c>
       <c r="B82">
-        <v>0.9474800494393351</v>
+        <v>1.234765707085181</v>
       </c>
       <c r="C82">
-        <v>-0.2702631782676469</v>
+        <v>0.3481272916779017</v>
       </c>
     </row>
     <row r="83">
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="B83">
-        <v>1.095060705593786</v>
+        <v>-0.04996305521597605</v>
       </c>
       <c r="C83">
-        <v>2.702270757306582</v>
+        <v>0.04915195573037562</v>
       </c>
     </row>
     <row r="84">
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="B84">
-        <v>0.3183931345683362</v>
+        <v>1.533346113565077</v>
       </c>
       <c r="C84">
-        <v>0.1860694542651659</v>
+        <v>0.6310467628601472</v>
       </c>
     </row>
     <row r="85">
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="B85">
-        <v>1.458539384435655</v>
+        <v>1.587860138997433</v>
       </c>
       <c r="C85">
-        <v>0.201295046577361</v>
+        <v>-0.8934796389018351</v>
       </c>
     </row>
     <row r="86">
@@ -1470,10 +1470,10 @@
         </is>
       </c>
       <c r="B86">
-        <v>-1.313059369100095</v>
+        <v>0.5989081518004361</v>
       </c>
       <c r="C86">
-        <v>0.6117020300846152</v>
+        <v>-0.04304183315665042</v>
       </c>
     </row>
     <row r="87">
@@ -1483,10 +1483,10 @@
         </is>
       </c>
       <c r="B87">
-        <v>0.1129858867328223</v>
+        <v>-1.911533711343614</v>
       </c>
       <c r="C87">
-        <v>1.403270441246864</v>
+        <v>0.8123156896991068</v>
       </c>
     </row>
     <row r="88">
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="B88">
-        <v>1.5549966372136</v>
+        <v>-0.9366828117915387</v>
       </c>
       <c r="C88">
-        <v>0.6989466912268537</v>
+        <v>-1.359303069453623</v>
       </c>
     </row>
     <row r="89">
@@ -1509,10 +1509,10 @@
         </is>
       </c>
       <c r="B89">
-        <v>1.404401299151637</v>
+        <v>0.8784460596039185</v>
       </c>
       <c r="C89">
-        <v>1.463572335069586</v>
+        <v>1.341036365169037</v>
       </c>
     </row>
     <row r="90">
@@ -1522,10 +1522,10 @@
         </is>
       </c>
       <c r="B90">
-        <v>-0.3776234082556957</v>
+        <v>-0.0389416705067132</v>
       </c>
       <c r="C90">
-        <v>0.03074799141457485</v>
+        <v>0.1758859876799568</v>
       </c>
     </row>
     <row r="91">
@@ -1535,10 +1535,10 @@
         </is>
       </c>
       <c r="B91">
-        <v>-0.393934530912802</v>
+        <v>0.08852970779527632</v>
       </c>
       <c r="C91">
-        <v>0.4533076079250663</v>
+        <v>-0.4735451900231312</v>
       </c>
     </row>
     <row r="92">
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="B92">
-        <v>-1.543964604265324</v>
+        <v>0.8289624827317523</v>
       </c>
       <c r="C92">
-        <v>-1.486118119033616</v>
+        <v>0.04196492181205003</v>
       </c>
     </row>
     <row r="93">
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="B93">
-        <v>-0.2341377279123268</v>
+        <v>0.237993621857557</v>
       </c>
       <c r="C93">
-        <v>-0.7451440280881279</v>
+        <v>-1.015982830004536</v>
       </c>
     </row>
     <row r="94">
@@ -1574,10 +1574,10 @@
         </is>
       </c>
       <c r="B94">
-        <v>1.088495334131377</v>
+        <v>0.1976249340494967</v>
       </c>
       <c r="C94">
-        <v>0.9767620716745289</v>
+        <v>-0.9104250151312995</v>
       </c>
     </row>
     <row r="95">
@@ -1587,10 +1587,10 @@
         </is>
       </c>
       <c r="B95">
-        <v>1.153026359341304</v>
+        <v>0.2637142788278662</v>
       </c>
       <c r="C95">
-        <v>1.53153936431766</v>
+        <v>0.2758842150398804</v>
       </c>
     </row>
     <row r="96">
@@ -1600,10 +1600,10 @@
         </is>
       </c>
       <c r="B96">
-        <v>-1.016649336547994</v>
+        <v>-0.8348443940326088</v>
       </c>
       <c r="C96">
-        <v>-0.9125158158580899</v>
+        <v>-0.5603360123443175</v>
       </c>
     </row>
     <row r="97">
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="B97">
-        <v>-0.4505397495657266</v>
+        <v>-0.1374504137096242</v>
       </c>
       <c r="C97">
-        <v>-0.3480822831921672</v>
+        <v>-0.9467775519585159</v>
       </c>
     </row>
     <row r="98">
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="B98">
-        <v>-2.297077049968329</v>
+        <v>0.1750254219618246</v>
       </c>
       <c r="C98">
-        <v>-0.1212547571867875</v>
+        <v>-0.1564933574764739</v>
       </c>
     </row>
     <row r="99">
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="B99">
-        <v>-0.754837956589699</v>
+        <v>0.8752035755253565</v>
       </c>
       <c r="C99">
-        <v>0.953667584159424</v>
+        <v>-0.334814270685322</v>
       </c>
     </row>
     <row r="100">
@@ -1652,10 +1652,10 @@
         </is>
       </c>
       <c r="B100">
-        <v>-0.2776721511720741</v>
+        <v>0.3459195502666141</v>
       </c>
       <c r="C100">
-        <v>-1.855844956379702</v>
+        <v>0.8550365207357629</v>
       </c>
     </row>
     <row r="101">
@@ -1665,10 +1665,10 @@
         </is>
       </c>
       <c r="B101">
-        <v>0.04067706814290185</v>
+        <v>-0.4508534755208761</v>
       </c>
       <c r="C101">
-        <v>-0.4192637578028243</v>
+        <v>0.3380743509717744</v>
       </c>
     </row>
     <row r="102">
@@ -1678,10 +1678,10 @@
         </is>
       </c>
       <c r="B102">
-        <v>0.0692245971225959</v>
+        <v>-1.746269677514864</v>
       </c>
       <c r="C102">
-        <v>1.462827339021686</v>
+        <v>-0.9564023434603944</v>
       </c>
     </row>
     <row r="103">
@@ -1691,10 +1691,10 @@
         </is>
       </c>
       <c r="B103">
-        <v>0.1107891651762049</v>
+        <v>0.04509466205134326</v>
       </c>
       <c r="C103">
-        <v>-1.46334319762106</v>
+        <v>-0.2305487788169548</v>
       </c>
     </row>
     <row r="104">
@@ -1704,10 +1704,10 @@
         </is>
       </c>
       <c r="B104">
-        <v>-1.122274408657496</v>
+        <v>0.8464045175413754</v>
       </c>
       <c r="C104">
-        <v>-0.5423064010431417</v>
+        <v>2.325263222222126</v>
       </c>
     </row>
     <row r="105">
@@ -1717,10 +1717,10 @@
         </is>
       </c>
       <c r="B105">
-        <v>0.693423338180677</v>
+        <v>0.6589037247964549</v>
       </c>
       <c r="C105">
-        <v>0.5923880978900034</v>
+        <v>0.4474553625053123</v>
       </c>
     </row>
     <row r="106">
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="B106">
-        <v>0.03963399817463659</v>
+        <v>-1.116922912689574</v>
       </c>
       <c r="C106">
-        <v>0.7342237966278169</v>
+        <v>-1.88590154706862</v>
       </c>
     </row>
     <row r="107">
@@ -1743,10 +1743,10 @@
         </is>
       </c>
       <c r="B107">
-        <v>-1.527797672951689</v>
+        <v>2.124423619949154</v>
       </c>
       <c r="C107">
-        <v>-0.7936656702009073</v>
+        <v>2.322556427496761</v>
       </c>
     </row>
     <row r="108">
@@ -1756,10 +1756,10 @@
         </is>
       </c>
       <c r="B108">
-        <v>-0.7342808026637492</v>
+        <v>-0.2849761368204544</v>
       </c>
       <c r="C108">
-        <v>-0.7498654621870577</v>
+        <v>-0.9189645399527347</v>
       </c>
     </row>
     <row r="109">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="B109">
-        <v>0.2141622888827859</v>
+        <v>-0.3541991774376073</v>
       </c>
       <c r="C109">
-        <v>0.7199481116728585</v>
+        <v>1.01363425392344</v>
       </c>
     </row>
     <row r="110">
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B110">
-        <v>-0.1416037578204682</v>
+        <v>1.413769488871456</v>
       </c>
       <c r="C110">
-        <v>-0.7070078573336104</v>
+        <v>0.4274513381271117</v>
       </c>
     </row>
     <row r="111">
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="B111">
-        <v>-0.2314206546396421</v>
+        <v>0.8117595546856566</v>
       </c>
       <c r="C111">
-        <v>-0.1840921230599234</v>
+        <v>-0.5283098143295986</v>
       </c>
     </row>
     <row r="112">
@@ -1808,10 +1808,10 @@
         </is>
       </c>
       <c r="B112">
-        <v>0.8243638943222309</v>
+        <v>1.164589408979083</v>
       </c>
       <c r="C112">
-        <v>0.2298130523266277</v>
+        <v>2.235837501085647</v>
       </c>
     </row>
     <row r="113">
@@ -1821,10 +1821,10 @@
         </is>
       </c>
       <c r="B113">
-        <v>-0.04186159898332083</v>
+        <v>-0.3758230743507229</v>
       </c>
       <c r="C113">
-        <v>0.760927108489163</v>
+        <v>-0.2637514771004705</v>
       </c>
     </row>
     <row r="114">
@@ -1834,10 +1834,10 @@
         </is>
       </c>
       <c r="B114">
-        <v>0.349461485248329</v>
+        <v>0.8105705724101205</v>
       </c>
       <c r="C114">
-        <v>1.222047736147756</v>
+        <v>0.6476818305445541</v>
       </c>
     </row>
     <row r="115">
@@ -1847,10 +1847,10 @@
         </is>
       </c>
       <c r="B115">
-        <v>-0.2551069095382485</v>
+        <v>0.5559110336029603</v>
       </c>
       <c r="C115">
-        <v>-0.0281107253498267</v>
+        <v>0.7985984391898725</v>
       </c>
     </row>
     <row r="116">
@@ -1860,10 +1860,10 @@
         </is>
       </c>
       <c r="B116">
-        <v>-0.3822020482220617</v>
+        <v>-0.8905193084850284</v>
       </c>
       <c r="C116">
-        <v>-0.2093002768848324</v>
+        <v>-0.5154875696894805</v>
       </c>
     </row>
     <row r="117">
@@ -1873,10 +1873,10 @@
         </is>
       </c>
       <c r="B117">
-        <v>-0.9928649321505945</v>
+        <v>0.359757769936346</v>
       </c>
       <c r="C117">
-        <v>-0.826624583592579</v>
+        <v>0.9712447334337003</v>
       </c>
     </row>
     <row r="118">
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="B118">
-        <v>-1.706344607749958</v>
+        <v>-0.2964706996480003</v>
       </c>
       <c r="C118">
-        <v>-0.5114433067064104</v>
+        <v>-0.06731573870483699</v>
       </c>
     </row>
     <row r="119">
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="B119">
-        <v>0.6863975282132693</v>
+        <v>0.5609479304023406</v>
       </c>
       <c r="C119">
-        <v>-0.1851111527041569</v>
+        <v>-0.6361603828626263</v>
       </c>
     </row>
     <row r="120">
@@ -1912,10 +1912,10 @@
         </is>
       </c>
       <c r="B120">
-        <v>-0.463083997134755</v>
+        <v>-0.1645812196483588</v>
       </c>
       <c r="C120">
-        <v>-0.3418157142595257</v>
+        <v>1.34778556184935</v>
       </c>
     </row>
     <row r="121">
@@ -1925,10 +1925,10 @@
         </is>
       </c>
       <c r="B121">
-        <v>1.436235922226744</v>
+        <v>1.567968716682173</v>
       </c>
       <c r="C121">
-        <v>0.09521865099163368</v>
+        <v>2.269324012197177</v>
       </c>
     </row>
     <row r="122">
@@ -1938,10 +1938,10 @@
         </is>
       </c>
       <c r="B122">
-        <v>-1.310876171626314</v>
+        <v>2.033584408258666</v>
       </c>
       <c r="C122">
-        <v>-0.1600542844044721</v>
+        <v>3.075409510697292</v>
       </c>
     </row>
     <row r="123">
@@ -1951,10 +1951,10 @@
         </is>
       </c>
       <c r="B123">
-        <v>0.2953212971766404</v>
+        <v>0.7182268166978473</v>
       </c>
       <c r="C123">
-        <v>-0.0679277447253008</v>
+        <v>0.8866207409446115</v>
       </c>
     </row>
     <row r="124">
@@ -1964,10 +1964,10 @@
         </is>
       </c>
       <c r="B124">
-        <v>0.8022568149090885</v>
+        <v>0.1385809938641987</v>
       </c>
       <c r="C124">
-        <v>0.07984552336118689</v>
+        <v>1.130188874882541</v>
       </c>
     </row>
     <row r="125">
@@ -1977,10 +1977,10 @@
         </is>
       </c>
       <c r="B125">
-        <v>0.6036931989401548</v>
+        <v>1.45387027255391</v>
       </c>
       <c r="C125">
-        <v>-1.048451967242812</v>
+        <v>2.405790222997314</v>
       </c>
     </row>
     <row r="126">
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="B126">
-        <v>0.4747839090871765</v>
+        <v>0.7368368855908075</v>
       </c>
       <c r="C126">
-        <v>0.7242368881967326</v>
+        <v>-0.3918740984642457</v>
       </c>
     </row>
     <row r="127">
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="B127">
-        <v>-0.1603823900305909</v>
+        <v>-0.6736381319367702</v>
       </c>
       <c r="C127">
-        <v>-2.454762700691611</v>
+        <v>-0.08192279383443901</v>
       </c>
     </row>
     <row r="128">
@@ -2016,10 +2016,10 @@
         </is>
       </c>
       <c r="B128">
-        <v>-0.2214758943537735</v>
+        <v>0.3980743000821302</v>
       </c>
       <c r="C128">
-        <v>0.1771686378790659</v>
+        <v>0.91074843530939</v>
       </c>
     </row>
     <row r="129">
@@ -2029,10 +2029,10 @@
         </is>
       </c>
       <c r="B129">
-        <v>-2.178059089862707</v>
+        <v>0.8294242168410157</v>
       </c>
       <c r="C129">
-        <v>-1.874740036549033</v>
+        <v>0.9438949508732541</v>
       </c>
     </row>
     <row r="130">
@@ -2042,10 +2042,10 @@
         </is>
       </c>
       <c r="B130">
-        <v>0.8717588165659939</v>
+        <v>2.305314992311648</v>
       </c>
       <c r="C130">
-        <v>1.133913216414109</v>
+        <v>-0.4500430678464521</v>
       </c>
     </row>
     <row r="131">
@@ -2055,10 +2055,10 @@
         </is>
       </c>
       <c r="B131">
-        <v>-0.8161013014220974</v>
+        <v>-0.1311853755279507</v>
       </c>
       <c r="C131">
-        <v>-0.8111071774727787</v>
+        <v>0.7048286602462694</v>
       </c>
     </row>
     <row r="132">
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="B132">
-        <v>0.339968480908013</v>
+        <v>0.08395779715154839</v>
       </c>
       <c r="C132">
-        <v>-0.4051974647403991</v>
+        <v>1.314514060051224</v>
       </c>
     </row>
     <row r="133">
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="B133">
-        <v>1.195934505944928</v>
+        <v>-0.5418415964865883</v>
       </c>
       <c r="C133">
-        <v>1.033535227487655</v>
+        <v>0.1498569628618193</v>
       </c>
     </row>
     <row r="134">
@@ -2094,10 +2094,10 @@
         </is>
       </c>
       <c r="B134">
-        <v>-1.700694510104042</v>
+        <v>-2.187728166351231</v>
       </c>
       <c r="C134">
-        <v>-0.4829285226717527</v>
+        <v>-0.5459813078469617</v>
       </c>
     </row>
     <row r="135">
@@ -2107,10 +2107,10 @@
         </is>
       </c>
       <c r="B135">
-        <v>0.06114561623090375</v>
+        <v>1.242336588884358</v>
       </c>
       <c r="C135">
-        <v>-0.2581583390613112</v>
+        <v>-0.05886010243128514</v>
       </c>
     </row>
     <row r="136">
@@ -2120,10 +2120,10 @@
         </is>
       </c>
       <c r="B136">
-        <v>0.4781441206648783</v>
+        <v>0.4236901791602475</v>
       </c>
       <c r="C136">
-        <v>1.487447612287545</v>
+        <v>0.9669094028876342</v>
       </c>
     </row>
     <row r="137">
@@ -2133,10 +2133,10 @@
         </is>
       </c>
       <c r="B137">
-        <v>-0.5975430812180441</v>
+        <v>-0.9334564940959834</v>
       </c>
       <c r="C137">
-        <v>0.899662809912528</v>
+        <v>-1.837281013849762</v>
       </c>
     </row>
     <row r="138">
@@ -2146,10 +2146,10 @@
         </is>
       </c>
       <c r="B138">
-        <v>0.6144673532693516</v>
+        <v>-0.2038543492184665</v>
       </c>
       <c r="C138">
-        <v>0.4384406560844578</v>
+        <v>-0.1100207491349772</v>
       </c>
     </row>
     <row r="139">
@@ -2159,10 +2159,10 @@
         </is>
       </c>
       <c r="B139">
-        <v>3.251148329057186</v>
+        <v>1.418327616264956</v>
       </c>
       <c r="C139">
-        <v>2.245650843530767</v>
+        <v>0.0743290894106029</v>
       </c>
     </row>
     <row r="140">
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="B140">
-        <v>2.227710096803234</v>
+        <v>-0.7757719961816769</v>
       </c>
       <c r="C140">
-        <v>-0.3264994817650801</v>
+        <v>-0.7197670305318153</v>
       </c>
     </row>
     <row r="141">
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="B141">
-        <v>1.514947438833115</v>
+        <v>1.091405249853836</v>
       </c>
       <c r="C141">
-        <v>0.001989190820803066</v>
+        <v>0.09809526920651335</v>
       </c>
     </row>
     <row r="142">
@@ -2198,10 +2198,10 @@
         </is>
       </c>
       <c r="B142">
-        <v>-1.038959079559241</v>
+        <v>-0.4911470782431873</v>
       </c>
       <c r="C142">
-        <v>-0.6778194020833563</v>
+        <v>0.7308357201352378</v>
       </c>
     </row>
     <row r="143">
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="B143">
-        <v>-2.145370741008611</v>
+        <v>0.9771779637559805</v>
       </c>
       <c r="C143">
-        <v>-0.7318015930755623</v>
+        <v>0.1532754827678503</v>
       </c>
     </row>
     <row r="144">
@@ -2224,10 +2224,10 @@
         </is>
       </c>
       <c r="B144">
-        <v>-0.4631063026299654</v>
+        <v>0.680816005749237</v>
       </c>
       <c r="C144">
-        <v>0.2025170151480125</v>
+        <v>1.237194858624638</v>
       </c>
     </row>
     <row r="145">
@@ -2237,10 +2237,10 @@
         </is>
       </c>
       <c r="B145">
-        <v>0.395755289388116</v>
+        <v>0.6242477184208612</v>
       </c>
       <c r="C145">
-        <v>-0.7135760408894495</v>
+        <v>1.206223051191282</v>
       </c>
     </row>
     <row r="146">
@@ -2250,10 +2250,10 @@
         </is>
       </c>
       <c r="B146">
-        <v>-0.04189983875790688</v>
+        <v>1.04555256607742</v>
       </c>
       <c r="C146">
-        <v>0.479663041900237</v>
+        <v>-0.7639372464108387</v>
       </c>
     </row>
     <row r="147">
@@ -2263,10 +2263,10 @@
         </is>
       </c>
       <c r="B147">
-        <v>2.562827134612387</v>
+        <v>-0.1194964380322016</v>
       </c>
       <c r="C147">
-        <v>1.777194846999919</v>
+        <v>0.4094992312656763</v>
       </c>
     </row>
     <row r="148">
@@ -2276,10 +2276,10 @@
         </is>
       </c>
       <c r="B148">
-        <v>0.9132753524358906</v>
+        <v>0.6409767921895144</v>
       </c>
       <c r="C148">
-        <v>-0.4806921865544376</v>
+        <v>0.1056550085248529</v>
       </c>
     </row>
     <row r="149">
@@ -2289,10 +2289,10 @@
         </is>
       </c>
       <c r="B149">
-        <v>-0.9169358641342744</v>
+        <v>1.810969323088023</v>
       </c>
       <c r="C149">
-        <v>0.172033574365442</v>
+        <v>-0.4691797842909011</v>
       </c>
     </row>
     <row r="150">
@@ -2302,10 +2302,10 @@
         </is>
       </c>
       <c r="B150">
-        <v>-0.3730138576728094</v>
+        <v>-1.642657771175522</v>
       </c>
       <c r="C150">
-        <v>0.7949187441973542</v>
+        <v>0.01514927417719403</v>
       </c>
     </row>
     <row r="151">
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="B151">
-        <v>-0.3787437546521416</v>
+        <v>0.4137499049934237</v>
       </c>
       <c r="C151">
-        <v>-1.114842045661622</v>
+        <v>1.315780665408823</v>
       </c>
     </row>
     <row r="152">
@@ -2328,10 +2328,10 @@
         </is>
       </c>
       <c r="B152">
-        <v>1.19176852909406</v>
+        <v>-0.4246693545529204</v>
       </c>
       <c r="C152">
-        <v>-0.7901020335021884</v>
+        <v>0.632666154122543</v>
       </c>
     </row>
     <row r="153">
@@ -2341,10 +2341,10 @@
         </is>
       </c>
       <c r="B153">
-        <v>-0.6812385216065361</v>
+        <v>0.8959318705346303</v>
       </c>
       <c r="C153">
-        <v>-0.3545901579269169</v>
+        <v>-0.7492922393984749</v>
       </c>
     </row>
     <row r="154">
@@ -2354,10 +2354,10 @@
         </is>
       </c>
       <c r="B154">
-        <v>0.5891483099169905</v>
+        <v>0.4979165963798848</v>
       </c>
       <c r="C154">
-        <v>0.1386522437984586</v>
+        <v>1.622594786680672</v>
       </c>
     </row>
     <row r="155">
@@ -2367,10 +2367,10 @@
         </is>
       </c>
       <c r="B155">
-        <v>0.478204118145752</v>
+        <v>0.0898466534929304</v>
       </c>
       <c r="C155">
-        <v>1.151482198391791</v>
+        <v>-1.084909216541327</v>
       </c>
     </row>
     <row r="156">
@@ -2380,10 +2380,10 @@
         </is>
       </c>
       <c r="B156">
-        <v>0.7171725572131731</v>
+        <v>0.4173424066933291</v>
       </c>
       <c r="C156">
-        <v>-0.5888629457649162</v>
+        <v>-1.110723854487126</v>
       </c>
     </row>
     <row r="157">
@@ -2393,10 +2393,10 @@
         </is>
       </c>
       <c r="B157">
-        <v>0.5546595685188426</v>
+        <v>-0.4703589186148497</v>
       </c>
       <c r="C157">
-        <v>0.3315901396195593</v>
+        <v>-0.7660067296989774</v>
       </c>
     </row>
     <row r="158">
@@ -2406,10 +2406,10 @@
         </is>
       </c>
       <c r="B158">
-        <v>-0.3557421848579198</v>
+        <v>1.026607395410127</v>
       </c>
       <c r="C158">
-        <v>1.020721176040426</v>
+        <v>-0.4065134741043669</v>
       </c>
     </row>
     <row r="159">
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="B159">
-        <v>-0.1538803855118036</v>
+        <v>-1.491602712197322</v>
       </c>
       <c r="C159">
-        <v>0.5423162987408767</v>
+        <v>-0.03479918020352502</v>
       </c>
     </row>
     <row r="160">
@@ -2432,10 +2432,10 @@
         </is>
       </c>
       <c r="B160">
-        <v>-0.6848279731999486</v>
+        <v>1.201533244047896</v>
       </c>
       <c r="C160">
-        <v>-0.6343217861198478</v>
+        <v>-2.621758852150007</v>
       </c>
     </row>
     <row r="161">
@@ -2445,10 +2445,10 @@
         </is>
       </c>
       <c r="B161">
-        <v>0.7347666351153601</v>
+        <v>-0.4807537133452595</v>
       </c>
       <c r="C161">
-        <v>0.03585237843022204</v>
+        <v>-1.875880797849655</v>
       </c>
     </row>
     <row r="162">
@@ -2458,10 +2458,10 @@
         </is>
       </c>
       <c r="B162">
-        <v>-1.140861229337099</v>
+        <v>-0.1151109117606294</v>
       </c>
       <c r="C162">
-        <v>1.331856801508807</v>
+        <v>0.8777822713567273</v>
       </c>
     </row>
     <row r="163">
@@ -2471,10 +2471,10 @@
         </is>
       </c>
       <c r="B163">
-        <v>0.3973161900457752</v>
+        <v>-0.1677160235493102</v>
       </c>
       <c r="C163">
-        <v>1.185657788393033</v>
+        <v>0.7686382021462798</v>
       </c>
     </row>
     <row r="164">
@@ -2484,10 +2484,10 @@
         </is>
       </c>
       <c r="B164">
-        <v>0.2994060957217329</v>
+        <v>-1.460004525863525</v>
       </c>
       <c r="C164">
-        <v>0.7893929239588288</v>
+        <v>-1.038549127391464</v>
       </c>
     </row>
     <row r="165">
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="B165">
-        <v>0.6607028378851842</v>
+        <v>1.423604843748976</v>
       </c>
       <c r="C165">
-        <v>-1.109505457490647</v>
+        <v>1.681370841027954</v>
       </c>
     </row>
     <row r="166">
@@ -2510,10 +2510,10 @@
         </is>
       </c>
       <c r="B166">
-        <v>-0.1703958413981465</v>
+        <v>1.381205124103777</v>
       </c>
       <c r="C166">
-        <v>-0.6418637252562973</v>
+        <v>-0.3491425695687168</v>
       </c>
     </row>
     <row r="167">
@@ -2523,10 +2523,10 @@
         </is>
       </c>
       <c r="B167">
-        <v>-1.192798165737271</v>
+        <v>0.3684998118697845</v>
       </c>
       <c r="C167">
-        <v>-2.305299124494278</v>
+        <v>0.8375269915498336</v>
       </c>
     </row>
     <row r="168">
@@ -2536,10 +2536,10 @@
         </is>
       </c>
       <c r="B168">
-        <v>0.7713237659145367</v>
+        <v>0.9601893563243252</v>
       </c>
       <c r="C168">
-        <v>-0.7625818853189004</v>
+        <v>1.801376314885127</v>
       </c>
     </row>
     <row r="169">
@@ -2549,10 +2549,10 @@
         </is>
       </c>
       <c r="B169">
-        <v>-0.4048111704249324</v>
+        <v>-2.138149659628124</v>
       </c>
       <c r="C169">
-        <v>-0.8787688021086286</v>
+        <v>-1.538827593363941</v>
       </c>
     </row>
     <row r="170">
@@ -2562,10 +2562,10 @@
         </is>
       </c>
       <c r="B170">
-        <v>-0.09272190076171871</v>
+        <v>-0.2116881331456099</v>
       </c>
       <c r="C170">
-        <v>1.378423429093832</v>
+        <v>-1.616246444499867</v>
       </c>
     </row>
     <row r="171">
@@ -2575,10 +2575,10 @@
         </is>
       </c>
       <c r="B171">
-        <v>0.482207799434057</v>
+        <v>0.8239057506014802</v>
       </c>
       <c r="C171">
-        <v>1.849738590975305</v>
+        <v>1.612266763730078</v>
       </c>
     </row>
     <row r="172">
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="B172">
-        <v>-0.6635224695495544</v>
+        <v>-1.07887681000948</v>
       </c>
       <c r="C172">
-        <v>0.6484679853214745</v>
+        <v>0.1717136821776012</v>
       </c>
     </row>
     <row r="173">
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="B173">
-        <v>0.6192695085457175</v>
+        <v>-0.4948507624306931</v>
       </c>
       <c r="C173">
-        <v>0.4796967264841621</v>
+        <v>-0.2756830929169533</v>
       </c>
     </row>
     <row r="174">
@@ -2614,10 +2614,10 @@
         </is>
       </c>
       <c r="B174">
-        <v>0.4402587856099317</v>
+        <v>-0.4206687412056969</v>
       </c>
       <c r="C174">
-        <v>-0.8169955052997242</v>
+        <v>-0.8179956531357299</v>
       </c>
     </row>
     <row r="175">
@@ -2627,10 +2627,10 @@
         </is>
       </c>
       <c r="B175">
-        <v>-0.9057404044990722</v>
+        <v>-1.819002637470944</v>
       </c>
       <c r="C175">
-        <v>-1.835655163038611</v>
+        <v>-1.37043294626489</v>
       </c>
     </row>
     <row r="176">
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="B176">
-        <v>1.837832810309876</v>
+        <v>0.473640764035655</v>
       </c>
       <c r="C176">
-        <v>1.298446920966842</v>
+        <v>-0.2450499348274931</v>
       </c>
     </row>
     <row r="177">
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="B177">
-        <v>-0.5023466697163955</v>
+        <v>-0.9261609774113615</v>
       </c>
       <c r="C177">
-        <v>-0.7554178266617648</v>
+        <v>-0.5145052540133833</v>
       </c>
     </row>
     <row r="178">
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="B178">
-        <v>0.9366535048577843</v>
+        <v>-0.4655360855918276</v>
       </c>
       <c r="C178">
-        <v>0.3507990440236176</v>
+        <v>-0.7036672846595233</v>
       </c>
     </row>
     <row r="179">
@@ -2679,10 +2679,10 @@
         </is>
       </c>
       <c r="B179">
-        <v>-1.587941188391617</v>
+        <v>1.437363473980869</v>
       </c>
       <c r="C179">
-        <v>-0.04596103652506067</v>
+        <v>1.40541207179456</v>
       </c>
     </row>
     <row r="180">
@@ -2692,10 +2692,10 @@
         </is>
       </c>
       <c r="B180">
-        <v>0.3821209772306817</v>
+        <v>0.421839691366323</v>
       </c>
       <c r="C180">
-        <v>1.317391473884238</v>
+        <v>-0.8408277835084021</v>
       </c>
     </row>
     <row r="181">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="B181">
-        <v>0.724708287039567</v>
+        <v>-1.206066927266604</v>
       </c>
       <c r="C181">
-        <v>-2.391033370701783</v>
+        <v>-0.9212655745037859</v>
       </c>
     </row>
     <row r="182">
@@ -2718,10 +2718,10 @@
         </is>
       </c>
       <c r="B182">
-        <v>1.753380840617198</v>
+        <v>-0.3600829280016669</v>
       </c>
       <c r="C182">
-        <v>1.659935991320685</v>
+        <v>1.676933986570015</v>
       </c>
     </row>
     <row r="183">
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="B183">
-        <v>1.856975311013263</v>
+        <v>0.7078907372292361</v>
       </c>
       <c r="C183">
-        <v>2.260893394038916</v>
+        <v>0.7044614809567564</v>
       </c>
     </row>
     <row r="184">
@@ -2744,10 +2744,10 @@
         </is>
       </c>
       <c r="B184">
-        <v>0.5654865962318735</v>
+        <v>-2.220721615608941</v>
       </c>
       <c r="C184">
-        <v>0.6176251706296951</v>
+        <v>-0.7462940768793721</v>
       </c>
     </row>
     <row r="185">
@@ -2757,10 +2757,10 @@
         </is>
       </c>
       <c r="B185">
-        <v>0.3962132955815322</v>
+        <v>1.272493446648173</v>
       </c>
       <c r="C185">
-        <v>-0.3200652476234262</v>
+        <v>1.784307088695623</v>
       </c>
     </row>
     <row r="186">
@@ -2770,10 +2770,10 @@
         </is>
       </c>
       <c r="B186">
-        <v>1.696905299611562</v>
+        <v>-0.3965571189221952</v>
       </c>
       <c r="C186">
-        <v>0.7679627827232113</v>
+        <v>1.02503148963001</v>
       </c>
     </row>
     <row r="187">
@@ -2783,10 +2783,10 @@
         </is>
       </c>
       <c r="B187">
-        <v>1.924060024746375</v>
+        <v>0.2609389261483372</v>
       </c>
       <c r="C187">
-        <v>0.03996125900192193</v>
+        <v>-1.501059160913975</v>
       </c>
     </row>
     <row r="188">
@@ -2796,10 +2796,10 @@
         </is>
       </c>
       <c r="B188">
-        <v>-2.195660744156049</v>
+        <v>-0.4203074138333404</v>
       </c>
       <c r="C188">
-        <v>-0.859064541160514</v>
+        <v>-0.8947439473503613</v>
       </c>
     </row>
     <row r="189">
@@ -2809,10 +2809,10 @@
         </is>
       </c>
       <c r="B189">
-        <v>0.3733290621635375</v>
+        <v>0.8293957881772054</v>
       </c>
       <c r="C189">
-        <v>-0.2160058986223571</v>
+        <v>-0.3275630251192837</v>
       </c>
     </row>
     <row r="190">
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="B190">
-        <v>-0.2000379511486452</v>
+        <v>-1.595723469294571</v>
       </c>
       <c r="C190">
-        <v>0.03117156259380911</v>
+        <v>-1.540595967138819</v>
       </c>
     </row>
     <row r="191">
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="B191">
-        <v>-0.9911556269127402</v>
+        <v>0.525375818550654</v>
       </c>
       <c r="C191">
-        <v>-0.06305092950741903</v>
+        <v>0.6470053880108766</v>
       </c>
     </row>
     <row r="192">
@@ -2848,10 +2848,10 @@
         </is>
       </c>
       <c r="B192">
-        <v>-1.923585850569531</v>
+        <v>-0.8655160113069056</v>
       </c>
       <c r="C192">
-        <v>-1.453181929837819</v>
+        <v>-1.304983745124557</v>
       </c>
     </row>
     <row r="193">
@@ -2861,10 +2861,10 @@
         </is>
       </c>
       <c r="B193">
-        <v>-1.912340670936129</v>
+        <v>-1.153734034364614</v>
       </c>
       <c r="C193">
-        <v>-0.8819943745261971</v>
+        <v>0.8224660546262008</v>
       </c>
     </row>
     <row r="194">
@@ -2874,10 +2874,10 @@
         </is>
       </c>
       <c r="B194">
-        <v>1.133810175161539</v>
+        <v>-0.2585352698324189</v>
       </c>
       <c r="C194">
-        <v>0.4071778243135791</v>
+        <v>1.131167131066243</v>
       </c>
     </row>
     <row r="195">
@@ -2887,10 +2887,10 @@
         </is>
       </c>
       <c r="B195">
-        <v>-0.6930302974039753</v>
+        <v>0.9041144979310989</v>
       </c>
       <c r="C195">
-        <v>0.7108601753143782</v>
+        <v>-0.1700009122117456</v>
       </c>
     </row>
     <row r="196">
@@ -2900,10 +2900,10 @@
         </is>
       </c>
       <c r="B196">
-        <v>1.482041375665245</v>
+        <v>-0.5112828379016823</v>
       </c>
       <c r="C196">
-        <v>2.396243907205895</v>
+        <v>1.168956165013991</v>
       </c>
     </row>
     <row r="197">
@@ -2913,10 +2913,10 @@
         </is>
       </c>
       <c r="B197">
-        <v>-1.899519502675624</v>
+        <v>-0.9173851941215413</v>
       </c>
       <c r="C197">
-        <v>-1.90527785823754</v>
+        <v>0.7474802116645708</v>
       </c>
     </row>
     <row r="198">
@@ -2926,10 +2926,10 @@
         </is>
       </c>
       <c r="B198">
-        <v>-0.409390247526657</v>
+        <v>-0.01545427443711509</v>
       </c>
       <c r="C198">
-        <v>0.8095609842390415</v>
+        <v>-0.4241553576881018</v>
       </c>
     </row>
     <row r="199">
@@ -2939,10 +2939,10 @@
         </is>
       </c>
       <c r="B199">
-        <v>1.125724052467121</v>
+        <v>-1.189458445638425</v>
       </c>
       <c r="C199">
-        <v>1.662677018341722</v>
+        <v>-1.442036100750112</v>
       </c>
     </row>
     <row r="200">
@@ -2952,10 +2952,10 @@
         </is>
       </c>
       <c r="B200">
-        <v>-0.1947004381979791</v>
+        <v>-0.9911298742443266</v>
       </c>
       <c r="C200">
-        <v>0.8819675528424508</v>
+        <v>-0.9095930770514202</v>
       </c>
     </row>
     <row r="201">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="B201">
-        <v>-1.072694800464682</v>
+        <v>-2.787365972900832</v>
       </c>
       <c r="C201">
-        <v>0.3311808422587021</v>
+        <v>-0.8695872879767111</v>
       </c>
     </row>
   </sheetData>
